--- a/quizzes/024_plant_life_cycle_quiz--quizzes.xlsx
+++ b/quizzes/024_plant_life_cycle_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>plant_life_cycle_quiz</t>
+          <t>What is your knowledge of plant life cycles?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>quiz_questions</t>
+          <t>how_plants_reproduce</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>quiz_questions</t>
+          <t>How do plants reproduce?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>quiz_question</t>
+          <t>root_function</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>quiz_question</t>
+          <t>What is the main function of roots?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>quiz_question</t>
+          <t>stages_of_plant_lifecycle</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>quiz_question_1</t>
+          <t>What are the three main stages of a plant's life cycle?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>quiz_answer</t>
+          <t>plant_growth</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>quiz_answer</t>
+          <t>How do plants grow from seed?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>quiz_answer</t>
+          <t>autotrophy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>quiz_answer_1</t>
+          <t>What is the term for a plant that produces its own food?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>quiz_answers</t>
+          <t>stem_function</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>quiz_answers</t>
+          <t>What is the function of the stem in a plant's life cycle?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>quiz_answers_1</t>
+          <t>cell_division</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>quiz_answers_1</t>
+          <t>In what stage of the plant life cycle is the process of cell division?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>quiz_answers_2</t>
+          <t>plant_growth_types</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>quiz_answers_2</t>
+          <t>What are the three main types of plant growth?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>quiz_answers_3</t>
+          <t>plant_nutrient_obtaining</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>quiz_answers_3</t>
+          <t>How do plants obtain nutrients?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>quiz_answers_4</t>
+          <t>leaf_function</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>quiz_answers_4</t>
+          <t>What is the primary role of the leaf in a plant's life cycle?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>quiz_answer_2</t>
+          <t>plant_type</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>quiz_answer_2</t>
+          <t>What is the term for a plant that grows from a single cell?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>quiz_answer_2</t>
+          <t>plant_type2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>quiz_answer_2_1</t>
+          <t>What is the term for a plant that grows from a multicellular body?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>quiz_question_2</t>
+          <t>plant_response</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>quiz_question_2</t>
+          <t>How do plants respond to environmental stresses?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>quiz_question_2</t>
+          <t>plant_type3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>quiz_question_2_1</t>
+          <t>What is the term for a plant that produces flowers?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>quiz_question_2</t>
+          <t>plant_type4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>quiz_question_2_1</t>
+          <t>What is the term for a plant that produces seeds?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>quiz_question_2</t>
+          <t>plant_type5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>quiz_question_2_2</t>
+          <t>What is the term for a plant that produces spores?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>quiz_question_2</t>
+          <t>plant_type6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>quiz_question_2_2</t>
+          <t>What is the term for a plant that produces gametes?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>quiz_answer_2</t>
+          <t>plant_type7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>quiz_answer_2_1</t>
+          <t>What is the term for a plant that produces vegetative propagation?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,136 +952,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>quiz_answer_2</t>
+          <t>additional_notes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>quiz_answer_2_2</t>
+          <t>Is there anything else you would like to add?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>quiz_answer_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>quiz_answer_3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>quiz_answer_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>quiz_answer_3_1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>quiz_answer_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>quiz_answer_4</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>quiz_answer_4</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>quiz_answer_4_1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>quiz_answer_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>quiz_answer_5</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +983,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,867 +1011,1156 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quiz_questions_choices</t>
+          <t>how_plants_reproduce_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>a._seed_germination</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>A. Seed germination</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quiz_questions_choices</t>
+          <t>how_plants_reproduce_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>b._vegetative_propagation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>B. Vegetative propagation</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quiz_questions_choices</t>
+          <t>how_plants_reproduce_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>c._somatic_embryogenesis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>C. Somatic embryogenesis</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>quiz_question_choices</t>
+          <t>how_plants_reproduce_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>d._apomictic_reproduction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>D. Apomictic reproduction</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quiz_question_choices</t>
+          <t>root_function_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>a._photosynthesis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>A. Photosynthesis</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quiz_question_choices</t>
+          <t>root_function_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>b._respiration</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>B. Respiration</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quiz_answer_choices</t>
+          <t>root_function_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>c._nutrient_and_water_absorption</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>C. Nutrient and water absorption</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quiz_answer_choices</t>
+          <t>root_function_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>d._support_and_storage</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>D. Support and storage</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quiz_answer_choices</t>
+          <t>stages_of_plant_lifecycle_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>a._seed,_sprout,_bloom</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>A. Seed, sprout, bloom</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>quiz_answers_choices</t>
+          <t>stages_of_plant_lifecycle_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>b._seed,_sprout,_leaf,_flower,_seed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>B. Seed, sprout, leaf, flower, seed</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quiz_answers_choices</t>
+          <t>stages_of_plant_lifecycle_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>c._seed,_root,_leaf,_flower,_seed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>C. Seed, root, leaf, flower, seed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>quiz_answers_choices</t>
+          <t>stages_of_plant_lifecycle_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>d._root,_sprout,_leaf,_flower,_seed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>D. Root, sprout, leaf, flower, seed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>quiz_answers_1_choices</t>
+          <t>plant_growth_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>a._through_photosynthesis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>A. Through photosynthesis</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>quiz_answers_1_choices</t>
+          <t>plant_growth_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>b._through_cell_division</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>B. Through cell division</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>quiz_answers_1_choices</t>
+          <t>plant_growth_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>c._through_mitosis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>C. Through mitosis</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>quiz_answers_2_choices</t>
+          <t>plant_growth_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>d._through_apical_meristem</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>D. Through apical meristem</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>quiz_answers_2_choices</t>
+          <t>autotrophy_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>a._autotrophic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>A. Autotrophic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>quiz_answers_2_choices</t>
+          <t>autotrophy_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>b._heterotrophic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>B. Heterotrophic</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>quiz_answers_3_choices</t>
+          <t>autotrophy_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>c._chemosynthetic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>C. Chemosynthetic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>quiz_answers_3_choices</t>
+          <t>autotrophy_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>d._photoheterotrophic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>D. Photoheterotrophic</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>quiz_answers_3_choices</t>
+          <t>stem_function_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>a._support</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>A. Support</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>quiz_answers_4_choices</t>
+          <t>stem_function_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>b._storage</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>B. Storage</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>quiz_answers_4_choices</t>
+          <t>stem_function_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>c._photosynthesis</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>C. Photosynthesis</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>quiz_answers_4_choices</t>
+          <t>stem_function_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>d._transport</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>D. Transport</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>quiz_question_2_choices</t>
+          <t>cell_division_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>a._seed_stage</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>A. Seed stage</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>quiz_question_2_choices</t>
+          <t>cell_division_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>b._root_stage</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>B. Root stage</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>quiz_question_2_choices</t>
+          <t>cell_division_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>c._leaf_stage</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>C. Leaf stage</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>quiz_question_2_choices</t>
+          <t>cell_division_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>d._reproductive_stage</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>D. Reproductive stage</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>quiz_question_2_choices</t>
+          <t>plant_growth_types_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>a._linear,_branching,_and_spiral</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>A. Linear, branching, and spiral</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>quiz_question_2_choices</t>
+          <t>plant_growth_types_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>b._linear,_branching,_and_spiral,_and_sympodial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>B. Linear, branching, and spiral, and sympodial</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>quiz_question_2_choices</t>
+          <t>plant_growth_types_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>c._linear,_branching,_and_spiral</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>C. Linear, branching, and spiral</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>quiz_question_2_choices</t>
+          <t>plant_growth_types_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>d._linear,_branching,_and_root</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>D. Linear, branching, and root</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>quiz_question_2_choices</t>
+          <t>plant_nutrient_obtaining_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>a._through_photosynthesis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>A. Through photosynthesis</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>quiz_question_2_choices</t>
+          <t>plant_nutrient_obtaining_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>b._through_heterotrophy</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>B. Through heterotrophy</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>quiz_question_2_choices</t>
+          <t>plant_nutrient_obtaining_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>c._through_autotrophy</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>C. Through autotrophy</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>quiz_question_2_choices</t>
+          <t>plant_nutrient_obtaining_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>d._through_symbiotic_relationship</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>D. Through symbiotic relationship</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>quiz_answer_3_choices</t>
+          <t>leaf_function_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>a._photosynthesis</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>A. Photosynthesis</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>quiz_answer_3_choices</t>
+          <t>leaf_function_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>b._respiration</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>B. Respiration</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>quiz_answer_3_choices</t>
+          <t>leaf_function_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>c._transpiration</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>C. Transpiration</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>quiz_answer_3_choices</t>
+          <t>leaf_function_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>d._support_and_storage</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>D. Support and storage</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>quiz_answer_3_choices</t>
+          <t>plant_type_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>a._heterosporous</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>A. Heterosporous</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>quiz_answer_3_choices</t>
+          <t>plant_type_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>b._monosporous</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>B. Monosporous</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quiz_answer_4_choices</t>
+          <t>plant_type_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>c._monosporic</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>C. Monosporic</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>quiz_answer_4_choices</t>
+          <t>plant_type_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>d._heterosporic</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>D. Heterosporic</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>quiz_answer_4_choices</t>
+          <t>plant_type2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>a._heterosporous</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>A. Heterosporous</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>quiz_answer_4_choices</t>
+          <t>plant_type2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>b._monosporous</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>B. Monosporous</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>quiz_answer_4_choices</t>
+          <t>plant_type2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>c._monosporic</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>C. Monosporic</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>quiz_answer_4_choices</t>
+          <t>plant_type2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>d._heterosporic</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>D. Heterosporic</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>quiz_answer_5_choices</t>
+          <t>plant_type3_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>a._angiosperm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>A. Angiosperm</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>quiz_answer_5_choices</t>
+          <t>plant_type3_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>b._gymnosperm</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>B. Gymnosperm</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>quiz_answer_5_choices</t>
+          <t>plant_type3_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>c._monocotyledon</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>C. Monocotyledon</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>plant_type3_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>d._dicotyledon</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>D. Dicotyledon</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>plant_type4_choices</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>a._angiosperm</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>A. Angiosperm</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>plant_type4_choices</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>b._gymnosperm</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>B. Gymnosperm</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>plant_type4_choices</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>c._monocotyledon</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>C. Monocotyledon</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>plant_type4_choices</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>d._dicotyledon</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>D. Dicotyledon</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>plant_type5_choices</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>a._pteridophyte</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>A. Pteridophyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>plant_type5_choices</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>b._spermatophyte</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>B. Spermatophyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>plant_type5_choices</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>c._bryophyte</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>C. Bryophyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>plant_type5_choices</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>d._pterosperm</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>D. Pterosperm</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>plant_type6_choices</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>a._heterosperm</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>A. Heterosperm</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>plant_type6_choices</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>b._heterosperm</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>B. Heterosperm</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>plant_type6_choices</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>c._monosperm</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>C. Monosperm</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>plant_type6_choices</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>d._monosperm</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>D. Monosperm</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>plant_type7_choices</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>a._buds</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>A. Buds</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>plant_type7_choices</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>b._rhizomes</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>B. Rhizomes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>plant_type7_choices</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>c._tubers</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>C. Tubers</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>plant_type7_choices</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>d._somatic</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>D. Somatic</t>
         </is>
       </c>
     </row>
